--- a/Economical analyzer.xlsx
+++ b/Economical analyzer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B738FDA-967A-4906-8B4D-69A258A4010C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADCCC6C-CF4B-417E-89FB-0D0FF83469BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3345" yWindow="2235" windowWidth="9150" windowHeight="12810" activeTab="2" xr2:uid="{0CC1A49D-AC71-41AE-A45D-C8FDA472BBE0}"/>
+    <workbookView xWindow="15990" yWindow="1290" windowWidth="9585" windowHeight="12810" firstSheet="4" activeTab="7" xr2:uid="{0CC1A49D-AC71-41AE-A45D-C8FDA472BBE0}"/>
   </bookViews>
   <sheets>
     <sheet name="AUD" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="27">
   <si>
     <t>Economic Data</t>
   </si>
@@ -70,9 +70,6 @@
     <t>Unemployment Rate (%)</t>
   </si>
   <si>
-    <t>March</t>
-  </si>
-  <si>
     <t>Retail Sales QoQ  (%)</t>
   </si>
   <si>
@@ -115,7 +112,7 @@
     <t>Next Rlease</t>
   </si>
   <si>
-    <t>5/13-May</t>
+    <t>april</t>
   </si>
 </sst>
 </file>
@@ -512,7 +509,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -557,16 +554,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>46105</v>
+        <v>46135</v>
       </c>
       <c r="C4">
+        <v>49.8</v>
+      </c>
+      <c r="D4">
+        <v>49.8</v>
+      </c>
+      <c r="E4">
         <v>51</v>
       </c>
-      <c r="D4">
-        <v>51</v>
-      </c>
-      <c r="E4">
-        <v>50.1</v>
+      <c r="F4" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -574,16 +574,16 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>46105</v>
+        <v>46135</v>
       </c>
       <c r="C5">
-        <v>52.8</v>
+        <v>46.3</v>
       </c>
       <c r="D5">
-        <v>52.8</v>
+        <v>46.3</v>
       </c>
       <c r="E5">
-        <v>46.6</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -591,19 +591,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>46106</v>
+        <v>46141</v>
       </c>
       <c r="C6">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D6">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6">
-        <v>3.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F6" s="2">
-        <v>46141</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -631,16 +631,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>46100</v>
+        <v>46128</v>
       </c>
       <c r="C8">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="D8">
-        <v>4.0999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="E8">
         <v>4.3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -678,7 +681,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -706,19 +709,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>46101</v>
+        <v>46136</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="D3">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="E3">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F3" s="2">
-        <v>46136</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -772,10 +775,10 @@
         <v>1.9</v>
       </c>
       <c r="E6">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="F6" s="2">
-        <v>46132</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -803,16 +806,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>46094</v>
+        <v>46123</v>
       </c>
       <c r="C8">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="D8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="E8">
         <v>6.7</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46150</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -850,7 +856,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -869,25 +875,28 @@
       <c r="E2">
         <v>0.1</v>
       </c>
+      <c r="F2" s="2">
+        <v>46156</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>46105</v>
+        <v>46136</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>-0.6</v>
       </c>
       <c r="D3">
-        <v>-0.8</v>
+        <v>0.2</v>
       </c>
       <c r="E3">
-        <v>-0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F3" s="2">
-        <v>46136</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -895,19 +904,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>46113</v>
+        <v>46135</v>
       </c>
       <c r="C4">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="D4">
-        <v>51.4</v>
+        <v>50.3</v>
       </c>
       <c r="E4">
-        <v>51</v>
+        <v>53.6</v>
       </c>
       <c r="F4" s="2">
-        <v>46135</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -915,19 +924,19 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>46108</v>
+        <v>46135</v>
       </c>
       <c r="C5">
-        <v>53.9</v>
+        <v>50.5</v>
       </c>
       <c r="D5">
-        <v>51.2</v>
+        <v>50</v>
       </c>
       <c r="E5">
-        <v>50.5</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2">
-        <v>46135</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -935,19 +944,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>46106</v>
+        <v>46134</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F6" s="2">
-        <v>46134</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -955,19 +964,19 @@
         <v>10</v>
       </c>
       <c r="B7" s="2">
-        <v>46106</v>
+        <v>46134</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="D7">
+        <v>1.8</v>
+      </c>
+      <c r="E7">
         <v>2.6</v>
       </c>
-      <c r="E7">
-        <v>1.7</v>
-      </c>
       <c r="F7" s="2">
-        <v>46134</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -975,19 +984,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>46100</v>
+        <v>46133</v>
       </c>
       <c r="C8">
         <v>5.2</v>
       </c>
       <c r="D8">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E8">
-        <v>5.2</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F8" s="2">
-        <v>46128</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1006,7 +1015,7 @@
   <cols>
     <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1025,8 +1034,8 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
+      <c r="F1" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1045,7 +1054,7 @@
       <c r="E2">
         <v>0.2</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="5">
         <v>46174</v>
       </c>
     </row>
@@ -1065,7 +1074,7 @@
       <c r="E3">
         <v>0.4</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="5">
         <v>46143</v>
       </c>
     </row>
@@ -1085,7 +1094,7 @@
       <c r="E4">
         <v>53.3</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="5">
         <v>46143</v>
       </c>
     </row>
@@ -1105,7 +1114,7 @@
       <c r="E5">
         <v>57.2</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="5">
         <v>46146</v>
       </c>
     </row>
@@ -1125,7 +1134,7 @@
       <c r="E6">
         <v>0.3</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="5">
         <v>46148</v>
       </c>
     </row>
@@ -1134,19 +1143,19 @@
         <v>10</v>
       </c>
       <c r="B7" s="5">
-        <v>46098</v>
+        <v>46128</v>
       </c>
       <c r="C7">
-        <v>-2.2000000000000002</v>
+        <v>-2.7</v>
       </c>
       <c r="D7">
-        <v>-2.2000000000000002</v>
+        <v>-2.7</v>
       </c>
       <c r="E7">
         <v>-2.7</v>
       </c>
-      <c r="F7" s="2">
-        <v>46128</v>
+      <c r="F7" s="5">
+        <v>46154</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1157,16 +1166,16 @@
         <v>46120</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
+        <v>3.1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>46149</v>
       </c>
     </row>
   </sheetData>
@@ -1201,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1209,16 +1218,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="2">
-        <v>46087</v>
+        <v>46142</v>
       </c>
       <c r="C2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E2">
-        <v>0.2</v>
+        <v>0.1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46155</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1245,57 +1257,58 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
+      <c r="B4" s="2">
+        <v>46135</v>
       </c>
       <c r="C4">
-        <v>50.8</v>
+        <v>51.6</v>
       </c>
       <c r="D4">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="E4">
-        <v>51.6</v>
+        <v>52.2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
+      <c r="B5" s="2">
+        <v>46133</v>
       </c>
       <c r="C5">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="D5">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E5">
-        <v>50.2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>46148</v>
-      </c>
+        <v>47.4</v>
+      </c>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="C6">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="D6">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="E6">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>46128</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1315,7 +1328,7 @@
         <v>-3</v>
       </c>
       <c r="F7" s="2">
-        <v>46120</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1323,16 +1336,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="C8">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="D8">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="E8">
         <v>6.2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46174</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1370,7 +1386,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,10 +1405,13 @@
       <c r="E2">
         <v>0.2</v>
       </c>
+      <c r="F2" s="2">
+        <v>46190</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2">
         <v>46075</v>
@@ -1405,6 +1424,9 @@
       </c>
       <c r="E3">
         <v>0.9</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,13 +1437,13 @@
         <v>46093</v>
       </c>
       <c r="C4">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="D4">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="E4">
-        <v>55</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1429,41 +1451,44 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>46096</v>
+        <v>46125</v>
       </c>
       <c r="C5">
-        <v>50.7</v>
+        <v>47.6</v>
       </c>
       <c r="D5">
-        <v>50.7</v>
+        <v>47.6</v>
       </c>
       <c r="E5">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46160</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>46044</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E6">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F6" s="2">
-        <v>46133</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
         <v>46070</v>
@@ -1496,6 +1521,9 @@
       </c>
       <c r="E8">
         <v>5.4</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46147</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1534,7 +1562,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1553,39 +1581,48 @@
       <c r="E2" s="6">
         <v>0.3</v>
       </c>
+      <c r="F2" s="2">
+        <v>46156</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="5">
-        <v>46111</v>
+        <v>46141</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="E3" s="6">
-        <v>-2</v>
+        <v>1.3</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46174</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
+      <c r="B4" s="5">
+        <v>46135</v>
       </c>
       <c r="C4">
-        <v>53</v>
+        <v>51.6</v>
       </c>
       <c r="D4">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="E4" s="6">
-        <v>51.6</v>
+        <v>54.9</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46163</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1593,16 +1630,16 @@
         <v>6</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C5">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
       <c r="D5">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="E5" s="6">
-        <v>53</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1610,19 +1647,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="5">
-        <v>46104</v>
+        <v>46136</v>
       </c>
       <c r="C6">
+        <v>1.3</v>
+      </c>
+      <c r="D6">
+        <v>1.3</v>
+      </c>
+      <c r="E6" s="6">
         <v>1.5</v>
       </c>
-      <c r="D6">
-        <v>1.5</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1.3</v>
-      </c>
       <c r="F6" s="2">
-        <v>46136</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1630,19 +1667,19 @@
         <v>10</v>
       </c>
       <c r="B7" s="5">
-        <v>46091</v>
+        <v>46122</v>
       </c>
       <c r="C7">
-        <v>2.2999999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="D7">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="E7" s="6">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="F7" s="2">
-        <v>46122</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1650,36 +1687,39 @@
         <v>11</v>
       </c>
       <c r="B8" s="5">
-        <v>46112</v>
+        <v>46140</v>
       </c>
       <c r="C8">
+        <v>2.6</v>
+      </c>
+      <c r="D8">
+        <v>2.6</v>
+      </c>
+      <c r="E8" s="6">
         <v>2.7</v>
       </c>
-      <c r="D8">
-        <v>2.7</v>
-      </c>
-      <c r="E8" s="6">
-        <v>2.6</v>
-      </c>
       <c r="F8" s="2">
-        <v>46140</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5">
-        <v>46090</v>
+        <v>46118</v>
       </c>
       <c r="C9">
-        <v>-2.6</v>
+        <v>-1</v>
       </c>
       <c r="D9">
-        <v>2.5</v>
+        <v>-0.7</v>
       </c>
       <c r="E9" s="6">
-        <v>-1</v>
+        <v>-1.8</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46150</v>
       </c>
     </row>
   </sheetData>
@@ -1714,7 +1754,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1722,19 +1762,19 @@
         <v>8</v>
       </c>
       <c r="B2" s="2">
-        <v>46094</v>
+        <v>46142</v>
       </c>
       <c r="C2">
-        <v>4.4000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>1.4</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E2">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>46121</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1742,21 +1782,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>46113</v>
+        <v>46133</v>
       </c>
       <c r="C3">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E3">
-        <v>0.6</v>
+        <v>1.7</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46156</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2">
         <v>46113</v>
@@ -1765,18 +1808,21 @@
         <v>52.4</v>
       </c>
       <c r="D4">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
       <c r="E4">
         <v>52.7</v>
       </c>
+      <c r="F4" s="2">
+        <v>46143</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2">
-        <v>46085</v>
+        <v>46118</v>
       </c>
       <c r="C5">
         <v>56.1</v>
@@ -1785,7 +1831,7 @@
         <v>54.8</v>
       </c>
       <c r="E5">
-        <v>52.4</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2">
         <v>46147</v>
@@ -1796,19 +1842,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="C6">
         <v>2.4</v>
       </c>
       <c r="D6">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="E6">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="F6" s="2">
-        <v>46122</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1816,44 +1862,44 @@
         <v>10</v>
       </c>
       <c r="B7" s="2">
-        <v>46099</v>
+        <v>46126</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="D7">
-        <v>0.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E7">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>46126</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2">
-        <v>46094</v>
+        <v>46142</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="E8">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="F8" s="2">
-        <v>46121</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2">
         <v>46115</v>
@@ -1862,15 +1908,18 @@
         <v>-133</v>
       </c>
       <c r="D9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E9">
         <v>178</v>
       </c>
+      <c r="F9" s="2">
+        <v>46150</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2">
         <v>46112</v>
@@ -1890,53 +1939,62 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>62</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46148</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>46114</v>
+        <v>46142</v>
       </c>
       <c r="C12">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D12">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E12">
-        <v>202</v>
+        <v>189</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46149</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2">
         <v>46115</v>
       </c>
       <c r="C13">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="D13">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="E13">
-        <v>0.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46150</v>
       </c>
     </row>
   </sheetData>

--- a/Economical analyzer.xlsx
+++ b/Economical analyzer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADCCC6C-CF4B-417E-89FB-0D0FF83469BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15029FA-DE63-42A1-8230-868B772B9CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15990" yWindow="1290" windowWidth="9585" windowHeight="12810" firstSheet="4" activeTab="7" xr2:uid="{0CC1A49D-AC71-41AE-A45D-C8FDA472BBE0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" activeTab="7" xr2:uid="{0CC1A49D-AC71-41AE-A45D-C8FDA472BBE0}"/>
   </bookViews>
   <sheets>
     <sheet name="AUD" sheetId="1" r:id="rId1"/>

--- a/Economical analyzer.xlsx
+++ b/Economical analyzer.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15029FA-DE63-42A1-8230-868B772B9CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE1033F-DA84-46D3-A235-BFCBF7606463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" activeTab="7" xr2:uid="{0CC1A49D-AC71-41AE-A45D-C8FDA472BBE0}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="16200" firstSheet="2" activeTab="3" xr2:uid="{0CC1A49D-AC71-41AE-A45D-C8FDA472BBE0}"/>
   </bookViews>
   <sheets>
     <sheet name="AUD" sheetId="1" r:id="rId1"/>
     <sheet name="CAD" sheetId="2" r:id="rId2"/>
     <sheet name="GBP" sheetId="3" r:id="rId3"/>
-    <sheet name="CHF" sheetId="4" r:id="rId4"/>
-    <sheet name="EUR" sheetId="6" r:id="rId5"/>
-    <sheet name="NZD" sheetId="7" r:id="rId6"/>
-    <sheet name="JPY" sheetId="8" r:id="rId7"/>
-    <sheet name="USD" sheetId="9" r:id="rId8"/>
+    <sheet name="EUR" sheetId="6" r:id="rId4"/>
+    <sheet name="JPY" sheetId="8" r:id="rId5"/>
+    <sheet name="USD" sheetId="9" r:id="rId6"/>
+    <sheet name="NZD" sheetId="7" r:id="rId7"/>
+    <sheet name="CHF" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="27">
   <si>
     <t>Economic Data</t>
   </si>
@@ -73,12 +73,6 @@
     <t>Retail Sales QoQ  (%)</t>
   </si>
   <si>
-    <t>CPI QoQ (%)</t>
-  </si>
-  <si>
-    <t>PPI QoQ(%)</t>
-  </si>
-  <si>
     <t>Household Spending (YoY%)</t>
   </si>
   <si>
@@ -113,6 +107,12 @@
   </si>
   <si>
     <t>april</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>PPI YoY(%)</t>
   </si>
 </sst>
 </file>
@@ -509,7 +509,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -611,7 +611,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="2">
-        <v>46052</v>
+        <v>46143</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -620,10 +620,10 @@
         <v>3.5</v>
       </c>
       <c r="E7">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>46143</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -681,7 +681,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -692,16 +692,16 @@
         <v>46112</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="F2" s="2">
-        <v>46142</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -729,19 +729,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="F4" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -752,13 +752,13 @@
         <v>46101</v>
       </c>
       <c r="C5">
-        <v>46.5</v>
+        <v>47.2</v>
       </c>
       <c r="D5">
-        <v>46.5</v>
+        <v>47.2</v>
       </c>
       <c r="E5">
-        <v>47.2</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -786,7 +786,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="2">
-        <v>46101</v>
+        <v>46135</v>
       </c>
       <c r="C7">
         <v>5.6</v>
@@ -795,10 +795,10 @@
         <v>5.6</v>
       </c>
       <c r="E7">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="F7" s="2">
-        <v>46135</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -856,7 +856,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1009,181 +1009,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9E5D81-8BC6-4161-8A3E-2F01DC73AFE6}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="5">
-        <v>46080</v>
-      </c>
-      <c r="C2">
-        <v>-0.4</v>
-      </c>
-      <c r="D2">
-        <v>0.2</v>
-      </c>
-      <c r="E2">
-        <v>0.2</v>
-      </c>
-      <c r="F2" s="5">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C3">
-        <v>-1.6</v>
-      </c>
-      <c r="D3">
-        <v>-1.6</v>
-      </c>
-      <c r="E3">
-        <v>0.4</v>
-      </c>
-      <c r="F3" s="5">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C4">
-        <v>47.4</v>
-      </c>
-      <c r="D4">
-        <v>47.2</v>
-      </c>
-      <c r="E4">
-        <v>53.3</v>
-      </c>
-      <c r="F4" s="5">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46113</v>
-      </c>
-      <c r="C5">
-        <v>54.2</v>
-      </c>
-      <c r="D5">
-        <v>54.5</v>
-      </c>
-      <c r="E5">
-        <v>57.2</v>
-      </c>
-      <c r="F5" s="5">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46114</v>
-      </c>
-      <c r="C6">
-        <v>0.1</v>
-      </c>
-      <c r="D6">
-        <v>0.5</v>
-      </c>
-      <c r="E6">
-        <v>0.3</v>
-      </c>
-      <c r="F6" s="5">
-        <v>46148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46128</v>
-      </c>
-      <c r="C7">
-        <v>-2.7</v>
-      </c>
-      <c r="D7">
-        <v>-2.7</v>
-      </c>
-      <c r="E7">
-        <v>-2.7</v>
-      </c>
-      <c r="F7" s="5">
-        <v>46154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46120</v>
-      </c>
-      <c r="C8">
-        <v>3.2</v>
-      </c>
-      <c r="D8">
-        <v>3.2</v>
-      </c>
-      <c r="E8">
-        <v>3.1</v>
-      </c>
-      <c r="F8" s="5">
-        <v>46149</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79918EC-CBFE-40B0-9003-96D9D9D8A351}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1210,7 +1035,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1238,19 +1063,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>46120</v>
+        <v>46149</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="D3">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E3">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" s="2">
-        <v>46149</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1308,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>46147</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1316,19 +1141,19 @@
         <v>10</v>
       </c>
       <c r="B7" s="2">
-        <v>46120</v>
+        <v>46148</v>
       </c>
       <c r="C7">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D7">
-        <v>-3</v>
+        <v>1.8</v>
       </c>
       <c r="E7">
-        <v>-3</v>
+        <v>2.1</v>
       </c>
       <c r="F7" s="2">
-        <v>46148</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1359,182 +1184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DF053D-CBED-4EF4-9655-ADBB226264F2}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2">
-        <v>46099</v>
-      </c>
-      <c r="C2">
-        <v>0.9</v>
-      </c>
-      <c r="D2">
-        <v>0.4</v>
-      </c>
-      <c r="E2">
-        <v>0.2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46190</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2">
-        <v>46075</v>
-      </c>
-      <c r="C3">
-        <v>1.9</v>
-      </c>
-      <c r="D3">
-        <v>0.6</v>
-      </c>
-      <c r="E3">
-        <v>0.9</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46093</v>
-      </c>
-      <c r="C4">
-        <v>54.8</v>
-      </c>
-      <c r="D4">
-        <v>54.8</v>
-      </c>
-      <c r="E4">
-        <v>53.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>46125</v>
-      </c>
-      <c r="C5">
-        <v>47.6</v>
-      </c>
-      <c r="D5">
-        <v>47.6</v>
-      </c>
-      <c r="E5">
-        <v>46</v>
-      </c>
-      <c r="F5" s="2">
-        <v>46160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
-        <v>46044</v>
-      </c>
-      <c r="C6">
-        <v>0.6</v>
-      </c>
-      <c r="D6">
-        <v>0.8</v>
-      </c>
-      <c r="E6">
-        <v>0.9</v>
-      </c>
-      <c r="F6" s="2">
-        <v>46223</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2">
-        <v>46070</v>
-      </c>
-      <c r="C7">
-        <v>0.6</v>
-      </c>
-      <c r="D7">
-        <v>0.7</v>
-      </c>
-      <c r="E7">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>46161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2">
-        <v>46056</v>
-      </c>
-      <c r="C8">
-        <v>5.3</v>
-      </c>
-      <c r="D8">
-        <v>5.3</v>
-      </c>
-      <c r="E8">
-        <v>5.4</v>
-      </c>
-      <c r="F8" s="2">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC556C0-8734-4BF7-A565-99C53019677B}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1562,7 +1212,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1582,7 +1232,7 @@
         <v>0.3</v>
       </c>
       <c r="F2" s="2">
-        <v>46156</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1602,7 +1252,7 @@
         <v>1.3</v>
       </c>
       <c r="F3" s="2">
-        <v>46174</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1616,10 +1266,10 @@
         <v>51.6</v>
       </c>
       <c r="D4">
-        <v>51.1</v>
+        <v>54.9</v>
       </c>
       <c r="E4" s="6">
-        <v>54.9</v>
+        <v>55.1</v>
       </c>
       <c r="F4" s="2">
         <v>46163</v>
@@ -1630,7 +1280,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>53.4</v>
@@ -1704,7 +1354,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5">
         <v>46118</v>
@@ -1727,7 +1377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81945AF8-1B91-4178-956B-91489910078D}">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1754,7 +1404,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1799,42 +1449,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C4">
-        <v>52.4</v>
+        <v>52.7</v>
       </c>
       <c r="D4">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="E4">
         <v>52.7</v>
       </c>
       <c r="F4" s="2">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>46118</v>
+        <v>46147</v>
       </c>
       <c r="C5">
-        <v>56.1</v>
+        <v>54</v>
       </c>
       <c r="D5">
-        <v>54.8</v>
+        <v>53.7</v>
       </c>
       <c r="E5">
-        <v>54</v>
+        <v>53.7</v>
       </c>
       <c r="F5" s="2">
-        <v>46147</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1879,7 +1529,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
         <v>46142</v>
@@ -1899,7 +1549,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2">
         <v>46115</v>
@@ -1919,67 +1569,67 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>46112</v>
+        <v>46147</v>
       </c>
       <c r="C10">
-        <v>7.24</v>
+        <v>6.88</v>
       </c>
       <c r="D10">
-        <v>6.89</v>
+        <v>6.83</v>
       </c>
       <c r="E10">
-        <v>6.88</v>
+        <v>6.87</v>
       </c>
       <c r="F10" s="2">
-        <v>46147</v>
+        <v>46175</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>46113</v>
+        <v>46148</v>
       </c>
       <c r="C11">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="E11">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="F11" s="2">
-        <v>46148</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="C12">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="D12">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E12">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="F12" s="2">
-        <v>46149</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2">
         <v>46115</v>
@@ -1995,6 +1645,479 @@
       </c>
       <c r="F13" s="2">
         <v>46150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DF053D-CBED-4EF4-9655-ADBB226264F2}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C2">
+        <v>0.9</v>
+      </c>
+      <c r="D2">
+        <v>0.4</v>
+      </c>
+      <c r="E2">
+        <v>0.2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46075</v>
+      </c>
+      <c r="C3">
+        <v>1.9</v>
+      </c>
+      <c r="D3">
+        <v>0.6</v>
+      </c>
+      <c r="E3">
+        <v>0.9</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C4">
+        <v>54.8</v>
+      </c>
+      <c r="D4">
+        <v>54.8</v>
+      </c>
+      <c r="E4">
+        <v>53.2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46125</v>
+      </c>
+      <c r="C5">
+        <v>47.6</v>
+      </c>
+      <c r="D5">
+        <v>47.6</v>
+      </c>
+      <c r="E5">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46132</v>
+      </c>
+      <c r="C6">
+        <v>3.1</v>
+      </c>
+      <c r="D6">
+        <v>2.9</v>
+      </c>
+      <c r="E6">
+        <v>3.1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46070</v>
+      </c>
+      <c r="C7">
+        <v>0.6</v>
+      </c>
+      <c r="D7">
+        <v>0.7</v>
+      </c>
+      <c r="E7">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C8">
+        <v>5.4</v>
+      </c>
+      <c r="D8">
+        <v>5.4</v>
+      </c>
+      <c r="E8">
+        <v>5.3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9E5D81-8BC6-4161-8A3E-2F01DC73AFE6}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5">
+        <v>46080</v>
+      </c>
+      <c r="C2">
+        <v>-0.4</v>
+      </c>
+      <c r="D2">
+        <v>0.2</v>
+      </c>
+      <c r="E2">
+        <v>0.2</v>
+      </c>
+      <c r="F2" s="5">
+        <v>46174</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46080</v>
+      </c>
+      <c r="I2">
+        <v>0.2</v>
+      </c>
+      <c r="J2">
+        <v>0.1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C3">
+        <v>-1.6</v>
+      </c>
+      <c r="D3">
+        <v>-1.6</v>
+      </c>
+      <c r="E3">
+        <v>0.4</v>
+      </c>
+      <c r="F3" s="5">
+        <v>46143</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="2">
+        <v>46143</v>
+      </c>
+      <c r="I3">
+        <v>0.6</v>
+      </c>
+      <c r="J3">
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="2">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C4">
+        <v>47.4</v>
+      </c>
+      <c r="D4">
+        <v>47.2</v>
+      </c>
+      <c r="E4">
+        <v>53.3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>46143</v>
+      </c>
+      <c r="G4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>46146</v>
+      </c>
+      <c r="I4">
+        <v>52</v>
+      </c>
+      <c r="J4">
+        <v>54.5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C5">
+        <v>54.2</v>
+      </c>
+      <c r="D5">
+        <v>54.5</v>
+      </c>
+      <c r="E5">
+        <v>57.2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>46146</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>57.2</v>
+      </c>
+      <c r="J5">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46114</v>
+      </c>
+      <c r="C6">
+        <v>0.1</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>46148</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="2">
+        <v>46147</v>
+      </c>
+      <c r="I6">
+        <v>0.3</v>
+      </c>
+      <c r="J6">
+        <v>0.6</v>
+      </c>
+      <c r="K6" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46128</v>
+      </c>
+      <c r="C7">
+        <v>-2.7</v>
+      </c>
+      <c r="D7">
+        <v>-2.7</v>
+      </c>
+      <c r="E7">
+        <v>-2.7</v>
+      </c>
+      <c r="F7" s="5">
+        <v>46154</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2">
+        <v>46128</v>
+      </c>
+      <c r="I7">
+        <v>-0.2</v>
+      </c>
+      <c r="J7">
+        <v>-2.7</v>
+      </c>
+      <c r="K7" s="2">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46120</v>
+      </c>
+      <c r="C8">
+        <v>3.2</v>
+      </c>
+      <c r="D8">
+        <v>3.2</v>
+      </c>
+      <c r="E8">
+        <v>3.1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>46149</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="2">
+        <v>46149</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8" s="2">
+        <v>46177</v>
       </c>
     </row>
   </sheetData>

--- a/Economical analyzer.xlsx
+++ b/Economical analyzer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\NEW SYSTEM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE1033F-DA84-46D3-A235-BFCBF7606463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298047AE-116B-4D5C-A25C-84425008BB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="16200" firstSheet="2" activeTab="3" xr2:uid="{0CC1A49D-AC71-41AE-A45D-C8FDA472BBE0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{0CC1A49D-AC71-41AE-A45D-C8FDA472BBE0}"/>
   </bookViews>
   <sheets>
     <sheet name="AUD" sheetId="1" r:id="rId1"/>
@@ -806,19 +806,19 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>46123</v>
+        <v>46150</v>
       </c>
       <c r="C8">
         <v>6.7</v>
       </c>
       <c r="D8">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="E8">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="F8" s="2">
-        <v>46150</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1121,19 +1121,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>46142</v>
+        <v>46175</v>
       </c>
       <c r="C6">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="F6" s="2">
-        <v>46162</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1163,17 +1163,17 @@
       <c r="B8" s="2">
         <v>46142</v>
       </c>
-      <c r="C8">
-        <v>6.3</v>
+      <c r="C8" s="2">
+        <v>46174</v>
       </c>
       <c r="D8">
         <v>6.2</v>
       </c>
       <c r="E8">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F8" s="2">
-        <v>46174</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1357,19 +1357,19 @@
         <v>13</v>
       </c>
       <c r="B9" s="5">
-        <v>46118</v>
+        <v>46154</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>-1.8</v>
       </c>
       <c r="D9">
-        <v>-0.7</v>
+        <v>-1.4</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.8</v>
+        <v>-2.9</v>
       </c>
       <c r="F9" s="2">
-        <v>46150</v>
+        <v>46178</v>
       </c>
     </row>
   </sheetData>
@@ -1412,20 +1412,18 @@
         <v>8</v>
       </c>
       <c r="B2" s="2">
-        <v>46142</v>
+        <v>46170</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>2.2999999999999998</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46170</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -1481,7 +1479,7 @@
         <v>53.7</v>
       </c>
       <c r="E5">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
       <c r="F5" s="2">
         <v>46176</v>
@@ -1492,19 +1490,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C6">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="D6">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="E6">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="F6" s="2">
-        <v>46154</v>
+        <v>46188</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1532,19 +1530,19 @@
         <v>16</v>
       </c>
       <c r="B8" s="2">
-        <v>46142</v>
+        <v>46170</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D8">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E8">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F8" s="2">
-        <v>46171</v>
+        <v>46198</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1552,19 +1550,19 @@
         <v>17</v>
       </c>
       <c r="B9" s="2">
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="C9">
-        <v>-133</v>
+        <v>178</v>
       </c>
       <c r="D9">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E9">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="F9" s="2">
-        <v>46150</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1572,19 +1570,19 @@
         <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>46147</v>
+        <v>46175</v>
       </c>
       <c r="C10">
-        <v>6.88</v>
+        <v>6.89</v>
       </c>
       <c r="D10">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="E10">
-        <v>6.87</v>
+        <v>7.62</v>
       </c>
       <c r="F10" s="2">
-        <v>46175</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1612,39 +1610,37 @@
         <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>46149</v>
+        <v>46170</v>
       </c>
       <c r="C12">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D12">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E12">
-        <v>200</v>
-      </c>
-      <c r="F12" s="2">
-        <v>46156</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="2">
-        <v>46115</v>
+        <v>46150</v>
       </c>
       <c r="C13">
+        <v>3.5</v>
+      </c>
+      <c r="D13">
         <v>3.8</v>
       </c>
-      <c r="D13">
-        <v>3.7</v>
-      </c>
       <c r="E13">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F13" s="2">
-        <v>46150</v>
+        <v>46178</v>
       </c>
     </row>
   </sheetData>
